--- a/education_surveys/015_cultural_diversity_and_immigration_survey--education_surveys.xlsx
+++ b/education_surveys/015_cultural_diversity_and_immigration_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'elementary'}</t>
+          <t>elementary</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Elementary'}</t>
+          <t>Elementary</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'High school'}</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Neither Agree nor Disagree'}</t>
+          <t>Neither Agree nor Disagree</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
